--- a/tame_output/ON/bt/strategyON_20240325.xlsx
+++ b/tame_output/ON/bt/strategyON_20240325.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410713</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.416754185778008</v>
+        <v>3.416754185778006</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.327531480858792</v>
+        <v>-2.326981738629224</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.155420509824825</v>
+        <v>2.155640406716652</v>
       </c>
       <c r="F1913" t="n">
         <v>0.8764953191285073</v>

--- a/tame_output/ON/bt/strategyON_20240325.xlsx
+++ b/tame_output/ON/bt/strategyON_20240325.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>105.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-60.1%</t>
+          <t>-62.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.5%</t>
+          <t>497.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-394.3%</t>
+          <t>-417.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.7%</t>
+          <t>-170.0%</t>
         </is>
       </c>
     </row>
@@ -45550,10 +45550,10 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.326981738629224</v>
+        <v>-2.56073431558321</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.155640406716652</v>
+        <v>2.062139375935057</v>
       </c>
       <c r="F1913" t="n">
         <v>0.8764953191285073</v>

--- a/tame_output/ON/bt/strategyON_20240325.xlsx
+++ b/tame_output/ON/bt/strategyON_20240325.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-68.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.2%</t>
+          <t>106.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.7%</t>
+          <t>121.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-566.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-43.1%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.5%</t>
+          <t>-62.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.8%</t>
+          <t>634.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-417.6%</t>
+          <t>-420.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-226.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-42.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>-1388.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-170.0%</t>
+          <t>-171.1%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -43802,10 +43802,10 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.4946297470876837</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.315985664012602</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43825,10 +43825,10 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.4464074802406002</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.300776739895436</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.2092759883908051</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.240865227653059</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.2143135791183916</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.241457704129432</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.1578439479420948</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.19761623328265</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.09207655789268276</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.172326886393356</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.07854107411597316</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.157540724870427</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>-0.003230826311778512</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.114914690654565</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>-0.07043993418365618</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.092796364339516</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>-0.06644848138846599</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.092217741576833</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.4645969123417266</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>2.930885260700591</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.6862188458998442</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.842102703876266</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.8942229042529214</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.763793225088961</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-1.164622866961807</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.650714696343395</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.503781244550329</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.508135644614435</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.831798466277808</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.397267045662212</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.828461719768836</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.406700494674369</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-2.195172771435382</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.261122466051483</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.580353162365454</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.105592848492317</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-2.924035935592117</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>1.969888862656268</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-3.281686285830465</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.822934781217186</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-3.288347226052613</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.822043331828587</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.720153019202401</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.635653902036076</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-4.046585548070144</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.493365665491069</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-4.048149699180447</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.491320596702913</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.411775944080761</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.352357658977029</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.409348879552042</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.352582999794348</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.817937656732721</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.187909032936836</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-5.230920140873815</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>1.017901471751859</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.647312015160812</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.8493387726459369</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-6.023989025690657</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.7089266591026782</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-6.037703890015768</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.6995402785183287</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.350528689260748</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.5728152788753378</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.355341727726085</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.5746690394184113</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.788690835836321</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.3973030916399138</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-7.171692224578952</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.2440004348212774</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.546677550750229</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.09657782032419648</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.906207873254231</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>-0.04188400537935388</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-8.232607901919245</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.1645279968881819</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-8.226131755125685</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.1588957875489889</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-8.222440830169274</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.1574194175664245</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.163088600104492</v>
+        <v>-8.426699005499138</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1281653284218693</v>
+        <v>-0.2336094905797279</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.323727626592857</v>
+        <v>-8.587338031987503</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1879383845327793</v>
+        <v>-0.2933825466906379</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.250257794925409</v>
+        <v>-8.513868200320054</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1431787503723787</v>
+        <v>-0.2486229125302373</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.425382212311952</v>
+        <v>-8.688992617706598</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1986732965794795</v>
+        <v>-0.3041174587373376</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.613655014677796</v>
+        <v>-8.877265420072442</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2812015824274132</v>
+        <v>-0.3866457445852713</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.633819656227343</v>
+        <v>-8.897430061621989</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.2959396298212082</v>
+        <v>-0.4013837919790664</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.140908962679956</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.863644103391168</v>
+        <v>-9.127254508785814</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.3867536188481817</v>
+        <v>-0.4921977810060403</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.303556499750117</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.800574871084828</v>
+        <v>-9.064185276479474</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.3588321972965312</v>
+        <v>-0.4642763594543893</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.332070062432351</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.748559357116015</v>
+        <v>-9.012169762510661</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3340356560226052</v>
+        <v>-0.4394798181804633</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.332070062432351</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.82985128667022</v>
+        <v>-9.093461692064865</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.3680276547430283</v>
+        <v>-0.4734718169008869</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.332070062432351</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410713</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.632581880942222</v>
+        <v>-8.896192286336868</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.2740664822869574</v>
+        <v>-0.3795106444448155</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.134800656704353</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.433429773705123</v>
+        <v>-8.697040179099769</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.2074567730388006</v>
+        <v>-0.3129009351966592</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.96947813075454</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.207584620985713</v>
+        <v>-8.471195026380357</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.1075396389148282</v>
+        <v>-0.2129838010726854</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.927551455167376</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.921309808663019</v>
+        <v>-8.184920214057662</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.00810943057030844</v>
+        <v>-0.0973347315875488</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.927551455167376</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.694513981589685</v>
+        <v>-7.958124386984329</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.1014615355617501</v>
+        <v>-0.003982626596107597</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.859437510545832</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.410605250660936</v>
+        <v>-7.67421565605558</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.2207587321718858</v>
+        <v>0.1153145700140286</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.859437510545832</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.163618000467983</v>
+        <v>-7.427228405862627</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.3098163698552017</v>
+        <v>0.204372207697344</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.61245026035288</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.899781133263915</v>
+        <v>-7.163391538658558</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.4054676354239217</v>
+        <v>0.300023473266064</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.61245026035288</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.632539332395518</v>
+        <v>-6.896149737790162</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.5105297952719066</v>
+        <v>0.4050856331140493</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.61245026035288</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.356730168995034</v>
+        <v>-6.620340574389678</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6205531456586395</v>
+        <v>0.5151089835007818</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.523430952074146</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.087662581228054</v>
+        <v>-6.351272986622698</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.7288486869109252</v>
+        <v>0.6234045247530675</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.254363364307167</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.823602642905258</v>
+        <v>-6.087213048299902</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.8212123460782914</v>
+        <v>0.7157681839204337</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9903034259843706</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.11652301940042</v>
+        <v>-5.380133424795064</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.101257161819926</v>
+        <v>0.9958129996620682</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9903034259843706</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.866881989414468</v>
+        <v>-5.130492394809112</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.201457197702148</v>
+        <v>1.09601303554429</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.7406623959984189</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.612340090073392</v>
+        <v>-4.875950495468036</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.302640778659335</v>
+        <v>1.197196616501478</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.4861204966573434</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.378858867843793</v>
+        <v>-4.642469273238437</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.403957696389027</v>
+        <v>1.298513534231169</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.2526392744277448</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.199150337699921</v>
+        <v>-4.462760743094565</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.472948898133617</v>
+        <v>1.367504735975759</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.1954677702650487</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.066874864069034</v>
+        <v>-4.330485269463678</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.521226574332998</v>
+        <v>1.415782412175141</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.06319229663416204</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.876275189395882</v>
+        <v>-4.139885594790526</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.600281504889896</v>
+        <v>1.494837342732039</v>
       </c>
       <c r="F1906" t="n">
         <v>0.1274073780389908</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430982</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.627275390712301</v>
+        <v>-3.890885796106945</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.712787765586987</v>
+        <v>1.60734360342913</v>
       </c>
       <c r="F1907" t="n">
         <v>0.3764071767225715</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.435896315851361</v>
+        <v>-3.699506721246005</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.661363465932145</v>
+        <v>1.555919303774287</v>
       </c>
       <c r="F1908" t="n">
         <v>0.5677862515835116</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.156869020195734</v>
+        <v>-3.420479425590378</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.821518726071482</v>
+        <v>1.716074563913624</v>
       </c>
       <c r="F1909" t="n">
         <v>0.5677862515835116</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.880130845524922</v>
+        <v>-3.143741250919566</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.935593007925801</v>
+        <v>1.830148845767944</v>
       </c>
       <c r="F1910" t="n">
         <v>0.7496029126934374</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.753238439089852</v>
+        <v>-3.016848844484496</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.977635984246351</v>
+        <v>1.872191822088493</v>
       </c>
       <c r="F1911" t="n">
         <v>0.8764953191285073</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.565650931179925</v>
+        <v>-2.829261336574569</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.045710375315228</v>
+        <v>1.940266213157371</v>
       </c>
       <c r="F1912" t="n">
         <v>0.8764953191285073</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.416754185778006</v>
+        <v>3.464000733703073</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.56073431558321</v>
+        <v>-2.587112943120711</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.062139375935057</v>
+        <v>2.051587924920057</v>
       </c>
       <c r="F1913" t="n">
         <v>0.8764953191285073</v>

--- a/tame_output/ON/bt/strategyON_20240325.xlsx
+++ b/tame_output/ON/bt/strategyON_20240325.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-33.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.1%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.3%</t>
+          <t>105.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.7%</t>
+          <t>120.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-566.2%</t>
+          <t>-539.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-43.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.1%</t>
+          <t>-62.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>634.6%</t>
+          <t>498.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-420.3%</t>
+          <t>-417.6%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,22 +1102,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-226.9%</t>
+          <t>-216.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1388.6%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-171.1%</t>
+          <t>-170.0%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-84.8%</t>
+          <t>-168.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1913"/>
+  <dimension ref="A1:G1914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.4946297470876837</v>
+        <v>0.7582401524823265</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.315985664012602</v>
+        <v>3.421429826170459</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43819,16 +43819,16 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4464074802406002</v>
+        <v>0.7100178856352429</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.300776739895436</v>
+        <v>3.406220902053293</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2092759883908051</v>
+        <v>0.4728863937854478</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.240865227653059</v>
+        <v>3.346309389810916</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2143135791183916</v>
+        <v>0.4779239845130344</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.241457704129432</v>
+        <v>3.346901866287289</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1578439479420948</v>
+        <v>0.4214543533367376</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.19761623328265</v>
+        <v>3.303060395440507</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.09207655789268276</v>
+        <v>0.3556869632873255</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.172326886393356</v>
+        <v>3.277771048551212</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.07854107411597316</v>
+        <v>0.3421514795106159</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.157540724870427</v>
+        <v>3.262984887028284</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.003230826311778512</v>
+        <v>0.2603795790828642</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.114914690654565</v>
+        <v>3.220358852812422</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.07043993418365618</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.092796364339516</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.06644848138846599</v>
+        <v>0.1971619240061768</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.092217741576833</v>
+        <v>3.19766190373469</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4645969123417266</v>
+        <v>-0.2009865069470839</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.930885260700591</v>
+        <v>3.036329422858449</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6862188458998442</v>
+        <v>-0.4226084405052014</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.842102703876266</v>
+        <v>2.947546866034124</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8942229042529214</v>
+        <v>-0.6306124988582786</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.763793225088961</v>
+        <v>2.869237387246818</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.164622866961807</v>
+        <v>-0.901012461567164</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.650714696343395</v>
+        <v>2.756158858501252</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.503781244550329</v>
+        <v>-1.240170839155686</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.508135644614435</v>
+        <v>2.613579806772292</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.831798466277808</v>
+        <v>-1.568188060883165</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.397267045662212</v>
+        <v>2.502711207820068</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.828461719768836</v>
+        <v>-1.564851314374194</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.406700494674369</v>
+        <v>2.512144656832226</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.195172771435382</v>
+        <v>-1.931562366040739</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.261122466051483</v>
+        <v>2.366566628209339</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.580353162365454</v>
+        <v>-2.316742756970812</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.105592848492317</v>
+        <v>2.211037010650174</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.924035935592117</v>
+        <v>-2.660425530197474</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.969888862656268</v>
+        <v>2.075333024814125</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.281686285830465</v>
+        <v>-3.018075880435823</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.822934781217186</v>
+        <v>1.928378943375043</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.288347226052613</v>
+        <v>-3.02473682065797</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.822043331828587</v>
+        <v>1.927487493986444</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.720153019202401</v>
+        <v>-3.456542613807758</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.635653902036076</v>
+        <v>1.741098064193933</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.046585548070144</v>
+        <v>-3.782975142675502</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.493365665491069</v>
+        <v>1.598809827648927</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.048149699180447</v>
+        <v>-3.784539293785805</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.491320596702913</v>
+        <v>1.596764758860771</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.411775944080761</v>
+        <v>-4.148165538686118</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.352357658977029</v>
+        <v>1.457801821134887</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.409348879552042</v>
+        <v>-4.145738474157399</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.352582999794348</v>
+        <v>1.458027161952206</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.817937656732721</v>
+        <v>-4.554327251338078</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.187909032936836</v>
+        <v>1.293353195094693</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.230920140873815</v>
+        <v>-4.967309735479172</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.017901471751859</v>
+        <v>1.123345633909716</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.647312015160812</v>
+        <v>-5.383701609766169</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8493387726459369</v>
+        <v>0.9547829348037946</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.023989025690657</v>
+        <v>-5.760378620296014</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7089266591026782</v>
+        <v>0.8143708212605358</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.037703890015768</v>
+        <v>-5.774093484621125</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6995402785183287</v>
+        <v>0.8049844406761864</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.350528689260748</v>
+        <v>-6.086918283866105</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5728152788753378</v>
+        <v>0.6782594410331955</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.355341727726085</v>
+        <v>-6.091731322331442</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5746690394184113</v>
+        <v>0.680113201576269</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.788690835836321</v>
+        <v>-6.525080430441678</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3973030916399138</v>
+        <v>0.5027472537977715</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.171692224578952</v>
+        <v>-6.908081819184309</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2440004348212774</v>
+        <v>0.3494445969791347</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.546677550750229</v>
+        <v>-7.283067145355586</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09657782032419648</v>
+        <v>0.2020219824820542</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.906207873254231</v>
+        <v>-7.642597467859588</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04188400537935388</v>
+        <v>0.0635601567785038</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.232607901919245</v>
+        <v>-7.968997496524601</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1645279968881819</v>
+        <v>-0.05908383473032419</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.226131755125685</v>
+        <v>-7.962521349731041</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1588957875489889</v>
+        <v>-0.05345162539113124</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.222440830169274</v>
+        <v>-7.95883042477463</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1574194175664245</v>
+        <v>-0.05197525540856685</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.426699005499138</v>
+        <v>-8.163088600104492</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2336094905797279</v>
+        <v>-0.1281653284218693</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.587338031987503</v>
+        <v>-8.323727626592857</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2933825466906379</v>
+        <v>-0.1879383845327793</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.513868200320054</v>
+        <v>-8.250257794925409</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2486229125302373</v>
+        <v>-0.1431787503723787</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.688992617706598</v>
+        <v>-8.425382212311952</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3041174587373376</v>
+        <v>-0.1986732965794795</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.877265420072442</v>
+        <v>-8.613655014677796</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3866457445852713</v>
+        <v>-0.2812015824274132</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.897430061621989</v>
+        <v>-8.633819656227343</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4013837919790664</v>
+        <v>-0.2959396298212082</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.140908962679956</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.127254508785814</v>
+        <v>-8.863644103391168</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4921977810060403</v>
+        <v>-0.3867536188481817</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.303556499750117</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.064185276479474</v>
+        <v>-8.800574871084828</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4642763594543893</v>
+        <v>-0.3588321972965312</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.332070062432351</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.012169762510661</v>
+        <v>-8.748559357116015</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4394798181804633</v>
+        <v>-0.3340356560226052</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.332070062432351</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.093461692064865</v>
+        <v>-8.82985128667022</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4734718169008869</v>
+        <v>-0.3680276547430283</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.332070062432351</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.896192286336868</v>
+        <v>-8.632581880942222</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.3795106444448155</v>
+        <v>-0.2740664822869574</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.134800656704353</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.697040179099769</v>
+        <v>-8.433429773705123</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.3129009351966592</v>
+        <v>-0.2074567730388006</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.96947813075454</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.471195026380357</v>
+        <v>-8.207584620985713</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.2129838010726854</v>
+        <v>-0.1075396389148282</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.927551455167376</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.184920214057662</v>
+        <v>-7.921309808663019</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.0973347315875488</v>
+        <v>0.00810943057030844</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.927551455167376</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.958124386984329</v>
+        <v>-7.694513981589685</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.003982626596107597</v>
+        <v>0.1014615355617501</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.859437510545832</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.67421565605558</v>
+        <v>-7.410605250660936</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.1153145700140286</v>
+        <v>0.2207587321718858</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.859437510545832</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.427228405862627</v>
+        <v>-7.163618000467983</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.204372207697344</v>
+        <v>0.3098163698552017</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.61245026035288</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.163391538658558</v>
+        <v>-6.899781133263915</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.300023473266064</v>
+        <v>0.4054676354239217</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.61245026035288</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.896149737790162</v>
+        <v>-6.632539332395518</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.4050856331140493</v>
+        <v>0.5105297952719066</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.61245026035288</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.620340574389678</v>
+        <v>-6.356730168995034</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.5151089835007818</v>
+        <v>0.6205531456586395</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.523430952074146</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.351272986622698</v>
+        <v>-6.087662581228054</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.6234045247530675</v>
+        <v>0.7288486869109252</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.254363364307167</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.087213048299902</v>
+        <v>-5.823602642905258</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.7157681839204337</v>
+        <v>0.8212123460782914</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9903034259843706</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.380133424795064</v>
+        <v>-5.11652301940042</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.9958129996620682</v>
+        <v>1.101257161819926</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9903034259843706</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.130492394809112</v>
+        <v>-4.866881989414468</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.09601303554429</v>
+        <v>1.201457197702148</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.7406623959984189</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.875950495468036</v>
+        <v>-4.612340090073392</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.197196616501478</v>
+        <v>1.302640778659335</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.4861204966573434</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.642469273238437</v>
+        <v>-4.378858867843793</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.298513534231169</v>
+        <v>1.403957696389027</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.2526392744277448</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.462760743094565</v>
+        <v>-4.199150337699921</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.367504735975759</v>
+        <v>1.472948898133617</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.1954677702650487</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.330485269463678</v>
+        <v>-4.066874864069034</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.415782412175141</v>
+        <v>1.521226574332998</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.06319229663416204</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.139885594790526</v>
+        <v>-3.876275189395882</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.494837342732039</v>
+        <v>1.600281504889896</v>
       </c>
       <c r="F1906" t="n">
         <v>0.1274073780389908</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.890885796106945</v>
+        <v>-3.627275390712301</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.60734360342913</v>
+        <v>1.712787765586987</v>
       </c>
       <c r="F1907" t="n">
         <v>0.3764071767225715</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.699506721246005</v>
+        <v>-3.435896315851361</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.555919303774287</v>
+        <v>1.661363465932145</v>
       </c>
       <c r="F1908" t="n">
         <v>0.5677862515835116</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.420479425590378</v>
+        <v>-3.156869020195734</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.716074563913624</v>
+        <v>1.821518726071482</v>
       </c>
       <c r="F1909" t="n">
         <v>0.5677862515835116</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.143741250919566</v>
+        <v>-2.880130845524922</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.830148845767944</v>
+        <v>1.935593007925801</v>
       </c>
       <c r="F1910" t="n">
         <v>0.7496029126934374</v>
@@ -45504,10 +45504,10 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.016848844484496</v>
+        <v>-2.753238439089852</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.872191822088493</v>
+        <v>1.977635984246351</v>
       </c>
       <c r="F1911" t="n">
         <v>0.8764953191285073</v>
@@ -45527,10 +45527,10 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.829261336574569</v>
+        <v>-2.565650931179925</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.940266213157371</v>
+        <v>2.045710375315228</v>
       </c>
       <c r="F1912" t="n">
         <v>0.8764953191285073</v>
@@ -45544,22 +45544,45 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.464000733703073</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.587112943120711</v>
+        <v>-2.56073431558321</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.051587924920057</v>
+        <v>2.062139375935057</v>
       </c>
       <c r="F1913" t="n">
         <v>0.8764953191285073</v>
       </c>
       <c r="G1913" t="n">
         <v>3.612686717959193</v>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" s="2" t="n">
+        <v>45376</v>
+      </c>
+      <c r="B1914" t="n">
+        <v>3.435168549648646</v>
+      </c>
+      <c r="C1914" t="n">
+        <v>2.781157665581926</v>
+      </c>
+      <c r="D1914" t="n">
+        <v>-2.56073431558321</v>
+      </c>
+      <c r="E1914" t="n">
+        <v>2.062139375935057</v>
+      </c>
+      <c r="F1914" t="n">
+        <v>0.8764953191285073</v>
+      </c>
+      <c r="G1914" t="n">
+        <v>2.774221462568294</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240325.xlsx
+++ b/tame_output/ON/bt/strategyON_20240325.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>19.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-29.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-69.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.1%</t>
+          <t>105.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.6%</t>
+          <t>121.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-566.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-43.1%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.6%</t>
+          <t>-64.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.1%</t>
+          <t>641.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-417.6%</t>
+          <t>-444.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-227.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-34.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-41.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>-1039.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-170.0%</t>
+          <t>-180.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.6%</t>
+          <t>-164.8%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.4913094603173802</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.314657549304481</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43819,16 +43819,16 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.4430871934702967</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.299448625187314</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.2059557016205016</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.239537112944938</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.2109932923480881</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.24012958942131</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.1545236611717913</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.196288118574529</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.08875627112237927</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.170998771685234</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.07522078734566967</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.156212610162306</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>-0.006551113082082005</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.113586575946444</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>-0.07376022095395968</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.091468249631395</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>-0.06976876815876948</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.090889626868711</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.4679171991120301</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>2.92955714599247</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.6895391326701477</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.840774589168145</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.8975431910232249</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.762465110380839</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-1.16794315373211</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.649386581635273</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.507101531320632</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.506807529906313</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.835118753048111</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.39593893095409</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.83178200653914</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.405372379966247</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-2.198493058205686</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.259794351343361</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.583673449135758</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.104264733784196</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-2.927356222362421</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>1.968560747948147</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-3.285006572600769</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.821606666509065</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-3.291667512822916</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.820715217120465</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.723473305972704</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.634325787327955</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-4.049905834840448</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.492037550782948</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-4.051469985950751</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.489992481994792</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.415096230851065</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.351029544268908</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.412669166322346</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.351254885086227</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.821257943503024</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.186580918228715</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-5.234240427644118</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>1.016573357043738</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.650632301931116</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.8480106579378162</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-6.02730931246096</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.7075985443945574</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-6.041024176786071</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.6982121638102079</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.353848976031051</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.571487164167217</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.358662014496388</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.5733409247102905</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.792011122606624</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.3959749769317931</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-7.175012511349255</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.2426723201131562</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.549997837520532</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.09524970561607571</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.909528160024534</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>-0.04321212008747466</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-8.235928188689547</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.1658561115963026</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-8.229452041895987</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.1602239022571097</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-8.225761116939577</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.1587475322745457</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.163088600104492</v>
+        <v>-8.43001929226944</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1281653284218693</v>
+        <v>-0.2349376052878487</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.323727626592857</v>
+        <v>-8.590658318757805</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1879383845327793</v>
+        <v>-0.2947106613987587</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.250257794925409</v>
+        <v>-8.517188487090356</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1431787503723787</v>
+        <v>-0.249951027238358</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.425382212311952</v>
+        <v>-8.6923129044769</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1986732965794795</v>
+        <v>-0.3054455734454584</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.613655014677796</v>
+        <v>-8.880585706842744</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2812015824274132</v>
+        <v>-0.3879738592933921</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.633819656227343</v>
+        <v>-8.900750348392291</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.2959396298212082</v>
+        <v>-0.4027119066871871</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.140908962679956</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.863644103391168</v>
+        <v>-9.130574795556116</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.3867536188481817</v>
+        <v>-0.4935258957141611</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.303556499750117</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.800574871084828</v>
+        <v>-9.067505563249776</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.3588321972965312</v>
+        <v>-0.4656044741625105</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.332070062432351</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.748559357116015</v>
+        <v>-9.015490049280963</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3340356560226052</v>
+        <v>-0.4408079328885841</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.332070062432351</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.82985128667022</v>
+        <v>-9.096781978835168</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.3680276547430283</v>
+        <v>-0.4747999316090077</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.332070062432351</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.632581880942222</v>
+        <v>-8.89951257310717</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.2740664822869574</v>
+        <v>-0.3808387591529363</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.134800656704353</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.433429773705123</v>
+        <v>-8.700360465870071</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.2074567730388006</v>
+        <v>-0.31422904990478</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.96947813075454</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.207584620985713</v>
+        <v>-8.474515313150661</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.1075396389148282</v>
+        <v>-0.2143119157808071</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.927551455167376</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.921309808663019</v>
+        <v>-8.188240500827966</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.00810943057030844</v>
+        <v>-0.09866284629567046</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.927551455167376</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.694513981589685</v>
+        <v>-7.961444673754633</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.1014615355617501</v>
+        <v>-0.005310741304229261</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.859437510545832</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.410605250660936</v>
+        <v>-7.677535942825884</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.2207587321718858</v>
+        <v>0.1139864553059069</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.859437510545832</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.163618000467983</v>
+        <v>-7.430548692632931</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.3098163698552017</v>
+        <v>0.2030440929892228</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.61245026035288</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.899781133263915</v>
+        <v>-7.166711825428862</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.4054676354239217</v>
+        <v>0.2986953585579424</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.61245026035288</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.632539332395518</v>
+        <v>-6.899470024560466</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.5105297952719066</v>
+        <v>0.4037575184059277</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.61245026035288</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.356730168995034</v>
+        <v>-6.623660861159982</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6205531456586395</v>
+        <v>0.5137808687926602</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.523430952074146</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.087662581228054</v>
+        <v>-6.354593273393002</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.7288486869109252</v>
+        <v>0.6220764100449458</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.254363364307167</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.823602642905258</v>
+        <v>-6.090533335070206</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.8212123460782914</v>
+        <v>0.7144400692123121</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9903034259843706</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.11652301940042</v>
+        <v>-5.383453711565368</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.101257161819926</v>
+        <v>0.9944848849539465</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9903034259843706</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.866881989414468</v>
+        <v>-5.133812681579416</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.201457197702148</v>
+        <v>1.094684920836169</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.7406623959984189</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.612340090073392</v>
+        <v>-4.87927078223834</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.302640778659335</v>
+        <v>1.195868501793356</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.4861204966573434</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.378858867843793</v>
+        <v>-4.645789560008741</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.403957696389027</v>
+        <v>1.297185419523048</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.2526392744277448</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.199150337699921</v>
+        <v>-4.466081029864869</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.472948898133617</v>
+        <v>1.366176621267638</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.1954677702650487</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860426</v>
+        <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.066874864069034</v>
+        <v>-4.333805556233982</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.521226574332998</v>
+        <v>1.414454297467019</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.06319229663416204</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.876275189395882</v>
+        <v>-4.14320588156083</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.600281504889896</v>
+        <v>1.493509228023917</v>
       </c>
       <c r="F1906" t="n">
         <v>0.1274073780389908</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.627275390712301</v>
+        <v>-3.894206082877249</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.712787765586987</v>
+        <v>1.606015488721008</v>
       </c>
       <c r="F1907" t="n">
         <v>0.3764071767225715</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.435896315851361</v>
+        <v>-3.702827008016309</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.661363465932145</v>
+        <v>1.554591189066165</v>
       </c>
       <c r="F1908" t="n">
         <v>0.5677862515835116</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.156869020195734</v>
+        <v>-3.423799712360682</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.821518726071482</v>
+        <v>1.714746449205502</v>
       </c>
       <c r="F1909" t="n">
         <v>0.5677862515835116</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.880130845524922</v>
+        <v>-3.14706153768987</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.935593007925801</v>
+        <v>1.828820731059822</v>
       </c>
       <c r="F1910" t="n">
         <v>0.7496029126934374</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.753238439089852</v>
+        <v>-3.0201691312548</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.977635984246351</v>
+        <v>1.870863707380372</v>
       </c>
       <c r="F1911" t="n">
         <v>0.8764953191285073</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.565650931179925</v>
+        <v>-2.832581623344873</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.045710375315228</v>
+        <v>1.938938098449249</v>
       </c>
       <c r="F1912" t="n">
         <v>0.8764953191285073</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.56073431558321</v>
+        <v>-2.827665007748158</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.062139375935057</v>
+        <v>1.955367099069079</v>
       </c>
       <c r="F1913" t="n">
         <v>0.8764953191285073</v>
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.435168549648646</v>
+        <v>3.480039076745897</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.781157665581926</v>
+        <v>2.818825183620354</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.56073431558321</v>
+        <v>-2.827665007748158</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.062139375935057</v>
+        <v>1.955367099069079</v>
       </c>
       <c r="F1914" t="n">
         <v>0.8764953191285073</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.774221462568294</v>
+        <v>2.811888980606722</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240325.xlsx
+++ b/tame_output/ON/bt/strategyON_20240325.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-69.4%</t>
+          <t>-68.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>106.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-566.6%</t>
+          <t>-566.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-64.3%</t>
+          <t>-63.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>641.9%</t>
+          <t>634.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-444.3%</t>
+          <t>-420.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-227.0%</t>
+          <t>-226.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1039.1%</t>
+          <t>-1388.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-180.7%</t>
+          <t>-171.1%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.4913094603173802</v>
+        <v>0.4946297470876837</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.314657549304481</v>
+        <v>3.315985664012602</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43819,16 +43819,16 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4430871934702967</v>
+        <v>0.4464074802406002</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.299448625187314</v>
+        <v>3.300776739895436</v>
       </c>
       <c r="F1838" t="n">
         <v>1.818391164641208</v>
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2059557016205016</v>
+        <v>0.2092759883908051</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.239537112944938</v>
+        <v>3.240865227653059</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2109932923480881</v>
+        <v>0.2143135791183916</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.24012958942131</v>
+        <v>3.241457704129432</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1545236611717913</v>
+        <v>0.1578439479420948</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.196288118574529</v>
+        <v>3.19761623328265</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.08875627112237927</v>
+        <v>0.09207655789268276</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.170998771685234</v>
+        <v>3.172326886393356</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.07522078734566967</v>
+        <v>0.07854107411597316</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.156212610162306</v>
+        <v>3.157540724870427</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.006551113082082005</v>
+        <v>-0.003230826311778512</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.113586575946444</v>
+        <v>3.114914690654565</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.07376022095395968</v>
+        <v>-0.07043993418365618</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.091468249631395</v>
+        <v>3.092796364339516</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.06976876815876948</v>
+        <v>-0.06644848138846599</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.090889626868711</v>
+        <v>3.092217741576833</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4679171991120301</v>
+        <v>-0.4645969123417266</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.92955714599247</v>
+        <v>2.930885260700591</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6895391326701477</v>
+        <v>-0.6862188458998442</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.840774589168145</v>
+        <v>2.842102703876266</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8975431910232249</v>
+        <v>-0.8942229042529214</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.762465110380839</v>
+        <v>2.763793225088961</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.16794315373211</v>
+        <v>-1.164622866961807</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.649386581635273</v>
+        <v>2.650714696343395</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.507101531320632</v>
+        <v>-1.503781244550329</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.506807529906313</v>
+        <v>2.508135644614435</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.835118753048111</v>
+        <v>-1.831798466277808</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.39593893095409</v>
+        <v>2.397267045662212</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.83178200653914</v>
+        <v>-1.828461719768836</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.405372379966247</v>
+        <v>2.406700494674369</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.198493058205686</v>
+        <v>-2.195172771435382</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.259794351343361</v>
+        <v>2.261122466051483</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.583673449135758</v>
+        <v>-2.580353162365454</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.104264733784196</v>
+        <v>2.105592848492317</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.927356222362421</v>
+        <v>-2.924035935592117</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.968560747948147</v>
+        <v>1.969888862656268</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.285006572600769</v>
+        <v>-3.281686285830465</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.821606666509065</v>
+        <v>1.822934781217186</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.291667512822916</v>
+        <v>-3.288347226052613</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.820715217120465</v>
+        <v>1.822043331828587</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.723473305972704</v>
+        <v>-3.720153019202401</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.634325787327955</v>
+        <v>1.635653902036076</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.049905834840448</v>
+        <v>-4.046585548070144</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.492037550782948</v>
+        <v>1.493365665491069</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.051469985950751</v>
+        <v>-4.048149699180447</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.489992481994792</v>
+        <v>1.491320596702913</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.415096230851065</v>
+        <v>-4.411775944080761</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.351029544268908</v>
+        <v>1.352357658977029</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.412669166322346</v>
+        <v>-4.409348879552042</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.351254885086227</v>
+        <v>1.352582999794348</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.821257943503024</v>
+        <v>-4.817937656732721</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.186580918228715</v>
+        <v>1.187909032936836</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.234240427644118</v>
+        <v>-5.230920140873815</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.016573357043738</v>
+        <v>1.017901471751859</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.650632301931116</v>
+        <v>-5.647312015160812</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8480106579378162</v>
+        <v>0.8493387726459369</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.02730931246096</v>
+        <v>-6.023989025690657</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7075985443945574</v>
+        <v>0.7089266591026782</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.041024176786071</v>
+        <v>-6.037703890015768</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6982121638102079</v>
+        <v>0.6995402785183287</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.353848976031051</v>
+        <v>-6.350528689260748</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.571487164167217</v>
+        <v>0.5728152788753378</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.358662014496388</v>
+        <v>-6.355341727726085</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5733409247102905</v>
+        <v>0.5746690394184113</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.792011122606624</v>
+        <v>-6.788690835836321</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3959749769317931</v>
+        <v>0.3973030916399138</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.175012511349255</v>
+        <v>-7.171692224578952</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2426723201131562</v>
+        <v>0.2440004348212774</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.549997837520532</v>
+        <v>-7.546677550750229</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09524970561607571</v>
+        <v>0.09657782032419648</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.909528160024534</v>
+        <v>-7.906207873254231</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04321212008747466</v>
+        <v>-0.04188400537935388</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.235928188689547</v>
+        <v>-8.232607901919245</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1658561115963026</v>
+        <v>-0.1645279968881819</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.229452041895987</v>
+        <v>-8.226131755125685</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1602239022571097</v>
+        <v>-0.1588957875489889</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.225761116939577</v>
+        <v>-8.222440830169274</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1587475322745457</v>
+        <v>-0.1574194175664245</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.43001929226944</v>
+        <v>-8.426699005499138</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2349376052878487</v>
+        <v>-0.2336094905797279</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.590658318757805</v>
+        <v>-8.587338031987503</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2947106613987587</v>
+        <v>-0.2933825466906379</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.517188487090356</v>
+        <v>-8.513868200320054</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.249951027238358</v>
+        <v>-0.2486229125302373</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.6923129044769</v>
+        <v>-8.688992617706598</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3054455734454584</v>
+        <v>-0.3041174587373376</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.880585706842744</v>
+        <v>-8.877265420072442</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3879738592933921</v>
+        <v>-0.3866457445852713</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.900750348392291</v>
+        <v>-8.897430061621989</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4027119066871871</v>
+        <v>-0.4013837919790664</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.140908962679956</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.130574795556116</v>
+        <v>-9.127254508785814</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4935258957141611</v>
+        <v>-0.4921977810060403</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.303556499750117</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.067505563249776</v>
+        <v>-9.064185276479474</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4656044741625105</v>
+        <v>-0.4642763594543893</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.332070062432351</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.015490049280963</v>
+        <v>-9.012169762510661</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4408079328885841</v>
+        <v>-0.4394798181804633</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.332070062432351</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.096781978835168</v>
+        <v>-9.093461692064865</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4747999316090077</v>
+        <v>-0.4734718169008869</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.332070062432351</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.89951257310717</v>
+        <v>-8.896192286336868</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.3808387591529363</v>
+        <v>-0.3795106444448155</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.134800656704353</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.700360465870071</v>
+        <v>-8.697040179099769</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.31422904990478</v>
+        <v>-0.3129009351966592</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.96947813075454</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.474515313150661</v>
+        <v>-8.471195026380357</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.2143119157808071</v>
+        <v>-0.2129838010726854</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.927551455167376</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.188240500827966</v>
+        <v>-8.184920214057662</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.09866284629567046</v>
+        <v>-0.0973347315875488</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.927551455167376</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.961444673754633</v>
+        <v>-7.958124386984329</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.005310741304229261</v>
+        <v>-0.003982626596107597</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.859437510545832</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.677535942825884</v>
+        <v>-7.67421565605558</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.1139864553059069</v>
+        <v>0.1153145700140286</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.859437510545832</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.430548692632931</v>
+        <v>-7.427228405862627</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.2030440929892228</v>
+        <v>0.204372207697344</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.61245026035288</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.166711825428862</v>
+        <v>-7.163391538658558</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.2986953585579424</v>
+        <v>0.300023473266064</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.61245026035288</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.899470024560466</v>
+        <v>-6.896149737790162</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.4037575184059277</v>
+        <v>0.4050856331140493</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.61245026035288</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.623660861159982</v>
+        <v>-6.620340574389678</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.5137808687926602</v>
+        <v>0.5151089835007818</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.523430952074146</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.354593273393002</v>
+        <v>-6.351272986622698</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.6220764100449458</v>
+        <v>0.6234045247530675</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.254363364307167</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.090533335070206</v>
+        <v>-6.087213048299902</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.7144400692123121</v>
+        <v>0.7157681839204337</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9903034259843706</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.383453711565368</v>
+        <v>-5.380133424795064</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.9944848849539465</v>
+        <v>0.9958129996620682</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9903034259843706</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.133812681579416</v>
+        <v>-5.130492394809112</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.094684920836169</v>
+        <v>1.09601303554429</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.7406623959984189</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.87927078223834</v>
+        <v>-4.875950495468036</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.195868501793356</v>
+        <v>1.197196616501478</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.4861204966573434</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.645789560008741</v>
+        <v>-4.642469273238437</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.297185419523048</v>
+        <v>1.298513534231169</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.2526392744277448</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.466081029864869</v>
+        <v>-4.462760743094565</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.366176621267638</v>
+        <v>1.367504735975759</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.1954677702650487</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.333805556233982</v>
+        <v>-4.330485269463678</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.414454297467019</v>
+        <v>1.415782412175141</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.06319229663416204</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471521857595</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.14320588156083</v>
+        <v>-4.139885594790526</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.493509228023917</v>
+        <v>1.494837342732039</v>
       </c>
       <c r="F1906" t="n">
         <v>0.1274073780389908</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430983</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.894206082877249</v>
+        <v>-3.890885796106945</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.606015488721008</v>
+        <v>1.60734360342913</v>
       </c>
       <c r="F1907" t="n">
         <v>0.3764071767225715</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.702827008016309</v>
+        <v>-3.699506721246005</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.554591189066165</v>
+        <v>1.555919303774287</v>
       </c>
       <c r="F1908" t="n">
         <v>0.5677862515835116</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.423799712360682</v>
+        <v>-3.420479425590378</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.714746449205502</v>
+        <v>1.716074563913624</v>
       </c>
       <c r="F1909" t="n">
         <v>0.5677862515835116</v>
@@ -45481,10 +45481,10 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.14706153768987</v>
+        <v>-3.143741250919566</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.828820731059822</v>
+        <v>1.830148845767944</v>
       </c>
       <c r="F1910" t="n">
         <v>0.7496029126934374</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.0201691312548</v>
+        <v>-3.016848844484496</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.870863707380372</v>
+        <v>1.872191822088493</v>
       </c>
       <c r="F1911" t="n">
         <v>0.8764953191285073</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.832581623344873</v>
+        <v>-2.829261336574569</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.938938098449249</v>
+        <v>1.940266213157371</v>
       </c>
       <c r="F1912" t="n">
         <v>0.8764953191285073</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.827665007748158</v>
+        <v>-2.587112943120711</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.955367099069079</v>
+        <v>2.051587924920057</v>
       </c>
       <c r="F1913" t="n">
         <v>0.8764953191285073</v>
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.480039076745897</v>
+        <v>3.480039076745896</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.818825183620354</v>
+        <v>2.818825183620355</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.827665007748158</v>
+        <v>-2.587112943120711</v>
       </c>
       <c r="E1914" t="n">
-        <v>1.955367099069079</v>
+        <v>2.051587924920057</v>
       </c>
       <c r="F1914" t="n">
         <v>0.8764953191285073</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.811888980606722</v>
+        <v>2.811888980606723</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240325.xlsx
+++ b/tame_output/ON/bt/strategyON_20240325.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.1%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.2%</t>
+          <t>106.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.6%</t>
+          <t>121.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-63.0%</t>
+          <t>-60.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>634.9%</t>
+          <t>635.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-420.3%</t>
+          <t>-398.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-42.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-171.1%</t>
+          <t>-162.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.8%</t>
+          <t>-85.3%</t>
         </is>
       </c>
     </row>
@@ -45570,19 +45570,19 @@
         <v>3.480039076745896</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.818825183620355</v>
+        <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.587112943120711</v>
+        <v>-2.368210304324853</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.051587924920057</v>
+        <v>2.133681100897595</v>
       </c>
       <c r="F1914" t="n">
         <v>0.8764953191285073</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.811888980606723</v>
+        <v>3.607218838418389</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240325.xlsx
+++ b/tame_output/ON/bt/strategyON_20240325.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>27.2%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-66.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.7%</t>
+          <t>106.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.7%</t>
+          <t>122.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-566.2%</t>
+          <t>-563.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-44.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>-61.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.3%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>635.8%</t>
+          <t>595.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-398.4%</t>
+          <t>-397.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-226.9%</t>
+          <t>-225.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.3%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.6%</t>
+          <t>-43.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-1388.6%</t>
+          <t>973.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-162.9%</t>
+          <t>-162.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-305.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-29.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>101.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.8%</t>
+          <t>-158.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-136.3%</t>
+          <t>-160.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-183.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-25.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-85.3%</t>
+          <t>-99.7%</t>
         </is>
       </c>
     </row>
@@ -43796,16 +43796,16 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.4946297470876837</v>
+        <v>0.7582401524823265</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.315985664012602</v>
+        <v>3.421429826170459</v>
       </c>
       <c r="F1837" t="n">
         <v>1.866613431488292</v>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4464074802406002</v>
+        <v>0.4707939870725982</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.300776739895436</v>
+        <v>3.310531342628235</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.579167266078564</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.070070531760081</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2092759883908051</v>
+        <v>0.2336624952228031</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.240865227653059</v>
+        <v>3.250619830385858</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.579167266078564</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.105011616257623</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2143135791183916</v>
+        <v>0.2387000859503897</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.241457704129432</v>
+        <v>3.251212306862231</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.634811722344881</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.136975730202751</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1578439479420948</v>
+        <v>0.1822304547740929</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.19761623328265</v>
+        <v>3.207370836015449</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.578342091168584</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.08184033312071</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.09207655789268276</v>
+        <v>0.1164630647246808</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.172326886393356</v>
+        <v>3.182081489126155</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.578342091168584</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.08285794225118</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.07854107411597316</v>
+        <v>0.1029275809479712</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.157540724870427</v>
+        <v>3.167295327603227</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.578342091168584</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.073485974238936</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.003230826311778512</v>
+        <v>0.02115568052021954</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.114914690654565</v>
+        <v>3.124669293387364</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.60537766457472</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.079790044237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.07043993418365618</v>
+        <v>-0.04605342735165813</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.092796364339516</v>
+        <v>3.102550967072315</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.60537766457472</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.084555361071558</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.06644848138846599</v>
+        <v>-0.04206197455646793</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.092217741576833</v>
+        <v>3.101972344309632</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.609369117369911</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.084775028867913</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4645969123417266</v>
+        <v>-0.4402104055097286</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.930885260700591</v>
+        <v>2.940639863433391</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.450444584979295</v>
+        <v>1.21122068641665</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.987347200938607</v>
+        <v>3.84381286180102</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6862188458998442</v>
+        <v>-0.661832339067846</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.842102703876266</v>
+        <v>2.851857306609066</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.412918451291926</v>
+        <v>1.173694552729281</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.964697737325107</v>
+        <v>3.82116339818752</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.8942229042529214</v>
+        <v>-0.8698363974209232</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.763793225088961</v>
+        <v>2.77354782782176</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.412918451291926</v>
+        <v>1.173694552729281</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.969589881879032</v>
+        <v>3.826055542741445</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.164622866961807</v>
+        <v>-1.140236360129809</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.650714696343395</v>
+        <v>2.660469299076194</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.14251848858304</v>
+        <v>0.9032945900203957</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.802431360591689</v>
+        <v>3.658897021454102</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.503781244550329</v>
+        <v>-1.479394737718331</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.508135644614435</v>
+        <v>2.517890247347234</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8033601109945183</v>
+        <v>0.5641362124318736</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.592020633345025</v>
+        <v>3.448486294207438</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.831798466277808</v>
+        <v>-1.80741195944581</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.397267045662212</v>
+        <v>2.407021648395011</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4753428892670392</v>
+        <v>0.2361189907043945</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.415548590047305</v>
+        <v>3.272014250909719</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.828461719768836</v>
+        <v>-1.804075212936838</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.406700494674369</v>
+        <v>2.416455097407168</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4780349216860705</v>
+        <v>0.2388110231234258</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.425262559907293</v>
+        <v>3.281728220769706</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.195172771435382</v>
+        <v>-2.170786264603384</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.261122466051483</v>
+        <v>2.270877068784282</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1113238700195249</v>
+        <v>-0.1279000285431198</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.206342320951098</v>
+        <v>3.062807981813511</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.580353162365454</v>
+        <v>-2.555966655533457</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.105592848492317</v>
+        <v>2.115347451225116</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1113238700195249</v>
+        <v>-0.1279000285431198</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.204884859763961</v>
+        <v>3.061350520626374</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.924035935592117</v>
+        <v>-2.899649428760119</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.969888862656268</v>
+        <v>1.979643465389067</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.003417817992306726</v>
+        <v>-0.235806080570338</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.141910352002246</v>
+        <v>2.998376012864659</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.281686285830465</v>
+        <v>-3.257299778998467</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.822934781217186</v>
+        <v>1.832689383949986</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.593456430808686</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.923426200515495</v>
+        <v>2.779891861377909</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.288347226052613</v>
+        <v>-3.263960719220615</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.822043331828587</v>
+        <v>1.831797934561386</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.593456430808686</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.925199127215755</v>
+        <v>2.781664788078168</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.720153019202401</v>
+        <v>-3.695766512370403</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.635653902036076</v>
+        <v>1.645408504768875</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4906500286873084</v>
+        <v>-0.729873927249953</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.829681516818399</v>
+        <v>2.686147177680812</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.046585548070144</v>
+        <v>-4.022199041238147</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.493365665491069</v>
+        <v>1.503120268223868</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.8123421777571012</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.768485341516201</v>
+        <v>2.624951002378614</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.048149699180447</v>
+        <v>-4.02376319234845</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.491320596702913</v>
+        <v>1.501075199435713</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.8123421777571012</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.767065933172166</v>
+        <v>2.623531594034579</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.411775944080761</v>
+        <v>-4.387389437248763</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.352357658977029</v>
+        <v>1.362112261709829</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6713399160615824</v>
+        <v>-0.910563814624227</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.714620511286132</v>
+        <v>2.571086172148545</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.409348879552042</v>
+        <v>-4.384962372720045</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.352582999794348</v>
+        <v>1.362337602527147</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.671672697868734</v>
+        <v>-0.9108965964313787</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713675357207673</v>
+        <v>2.570141018070086</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.817937656732721</v>
+        <v>-4.793551149900724</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.187909032936836</v>
+        <v>1.197663635669635</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.319485373612057</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.467283634914025</v>
+        <v>2.323749295776438</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.230920140873815</v>
+        <v>-5.206533634041818</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.017901471751859</v>
+        <v>1.027656074484658</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.319485373612057</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462469067385485</v>
+        <v>2.318934728247898</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.647312015160812</v>
+        <v>-5.622925508328815</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8493387726459369</v>
+        <v>0.8590933753787362</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.319485373612057</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460463117994363</v>
+        <v>2.316928778856776</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.023989025690657</v>
+        <v>-5.999602518858659</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7089266591026782</v>
+        <v>0.7186812618354774</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.319485373612057</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.470721808663042</v>
+        <v>2.327187469525455</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.037703890015768</v>
+        <v>-6.013317383183771</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6995402785183287</v>
+        <v>0.7092948812511284</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.319485373612057</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466821373808737</v>
+        <v>2.32328703467115</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.350528689260748</v>
+        <v>-6.32614218242875</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5728152788753378</v>
+        <v>0.5825698816081375</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.319485373612057</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.465226293863738</v>
+        <v>2.321691954726151</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.355341727726085</v>
+        <v>-6.330955220894087</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5746690394184113</v>
+        <v>0.5844236421512106</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.321032008314843</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.468077288971275</v>
+        <v>2.324542949833687</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.788690835836321</v>
+        <v>-6.764304329004323</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.3973030916399138</v>
+        <v>0.4070576943727131</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.321032008314843</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.464050984436871</v>
+        <v>2.320516645299285</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.171692224578952</v>
+        <v>-7.147305717746955</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2440004348212774</v>
+        <v>0.2537550375540767</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.321032008314843</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.463948883115287</v>
+        <v>2.320414543977701</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.546677550750229</v>
+        <v>-7.522291043918232</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09657782032419648</v>
+        <v>0.1063324230569958</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.69601733448612</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.241529203383951</v>
+        <v>2.097994864246364</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.906207873254231</v>
+        <v>-7.881821366422233</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04188400537935388</v>
+        <v>-0.03212940264655462</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.69601733448612</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.246879506682001</v>
+        <v>2.103345167544414</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.232607901919245</v>
+        <v>-8.208221395087246</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1645279968881819</v>
+        <v>-0.1547733941553822</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.783193464588488</v>
+        <v>-2.022417363151133</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.058955509440171</v>
+        <v>1.915421170302584</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.226131755125685</v>
+        <v>-8.201745248293687</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1588957875489889</v>
+        <v>-0.1491411848161897</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.776717317794929</v>
+        <v>-2.015941216357573</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.065882948138076</v>
+        <v>1.922348609000489</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.222440830169274</v>
+        <v>-8.198054323337276</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1574194175664245</v>
+        <v>-0.1476648148336253</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.776717317794929</v>
+        <v>-2.015941216357573</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.065882948138076</v>
+        <v>1.922348609000489</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.426699005499138</v>
+        <v>-8.40231249866714</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2336094905797279</v>
+        <v>-0.2238548878469286</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.904356262408918</v>
+        <v>-2.143580160971562</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.994812778488325</v>
+        <v>1.851278439350738</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.587338031987503</v>
+        <v>-8.562951525155505</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2933825466906379</v>
+        <v>-0.2836279439578386</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.019089735411313</v>
+        <v>-2.258313633973958</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.930455249171323</v>
+        <v>1.786920910033736</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.513868200320054</v>
+        <v>-8.489481693488056</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2486229125302373</v>
+        <v>-0.2388683097974376</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.945619903743865</v>
+        <v>-2.18484380230651</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.989908849665214</v>
+        <v>1.846374510527627</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.688992617706598</v>
+        <v>-8.664606110874599</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3041174587373376</v>
+        <v>-0.2943628560045384</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.120744321130409</v>
+        <v>-2.359968219693053</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.899389419980804</v>
+        <v>1.755855080843217</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.877265420072442</v>
+        <v>-8.852878913240444</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3866457445852713</v>
+        <v>-0.3768911418524721</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.120744321130409</v>
+        <v>-2.359968219693053</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.892170255079208</v>
+        <v>1.748635915941621</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.897430061621989</v>
+        <v>-8.873043554789991</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4013837919790664</v>
+        <v>-0.3916291892462671</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.140908962679956</v>
+        <v>-2.380132861242601</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.873399279375503</v>
+        <v>1.729864940237916</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.127254508785814</v>
+        <v>-9.102868001953816</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4921977810060403</v>
+        <v>-0.4824431782732406</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.303556499750117</v>
+        <v>-2.542780398312761</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.776926546971963</v>
+        <v>1.633392207834376</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.064185276479474</v>
+        <v>-9.039798769647476</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4642763594543893</v>
+        <v>-0.45452175672159</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.332070062432351</v>
+        <v>-2.571293960994996</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.762512137991737</v>
+        <v>1.61897779885415</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.012169762510661</v>
+        <v>-8.987783255678663</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4394798181804633</v>
+        <v>-0.4297252154476641</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.332070062432351</v>
+        <v>-2.571293960994996</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.766502473678138</v>
+        <v>1.622968134540551</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.093461692064865</v>
+        <v>-9.069075185232867</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4734718169008869</v>
+        <v>-0.4637172141680876</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.332070062432351</v>
+        <v>-2.571293960994996</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.765027246779396</v>
+        <v>1.621492907641809</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.896192286336868</v>
+        <v>-8.87180577950487</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.3795106444448155</v>
+        <v>-0.3697560417120163</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.134800656704353</v>
+        <v>-2.374024555266998</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.898442300381068</v>
+        <v>1.754907961243481</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.697040179099769</v>
+        <v>-8.672653672267771</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.3129009351966592</v>
+        <v>-0.3031463324638595</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.96947813075454</v>
+        <v>-2.208702029317184</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.984584682304273</v>
+        <v>1.841050343166686</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.471195026380357</v>
+        <v>-8.446808519548359</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.2129838010726854</v>
+        <v>-0.2032291983398862</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.927551455167376</v>
+        <v>-2.166775353730021</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.019319760692779</v>
+        <v>1.875785421555193</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.184920214057662</v>
+        <v>-8.160533707225664</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.0973347315875488</v>
+        <v>-0.08758012885474953</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.927551455167376</v>
+        <v>-2.166775353730021</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.020458905248838</v>
+        <v>1.876924566111251</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.958124386984329</v>
+        <v>-7.93373788015233</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.003982626596107597</v>
+        <v>0.00577197613669167</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.859437510545832</v>
+        <v>-2.098661409108476</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.063961046183873</v>
+        <v>1.920426707046285</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.67421565605558</v>
+        <v>-7.649829149223581</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.1153145700140286</v>
+        <v>0.1250691727468278</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.859437510545832</v>
+        <v>-2.098661409108476</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.069694750422509</v>
+        <v>1.926160411284922</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.427228405862627</v>
+        <v>-7.402841899030629</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.204372207697344</v>
+        <v>0.2141268104301437</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.61245026035288</v>
+        <v>-1.851674158915524</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.208149838144415</v>
+        <v>2.064615499006828</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-7.163391538658558</v>
+        <v>-7.13900503182656</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.300023473266064</v>
+        <v>0.3097780759988633</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.61245026035288</v>
+        <v>-1.851674158915524</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.198266356831507</v>
+        <v>2.054732017693921</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.896149737790162</v>
+        <v>-6.871763230958163</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.4050856331140493</v>
+        <v>0.4148402358468486</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.61245026035288</v>
+        <v>-1.851674158915524</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.196431796332134</v>
+        <v>2.052897457194547</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.620340574389678</v>
+        <v>-6.595954067557679</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.5151089835007818</v>
+        <v>0.5248635862335811</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.523430952074146</v>
+        <v>-1.762654850636791</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.249543066325913</v>
+        <v>2.106008727188327</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.351272986622698</v>
+        <v>-6.3268864797907</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.6234045247530675</v>
+        <v>0.6331591274858668</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.254363364307167</v>
+        <v>-1.493587262869811</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.411652125131594</v>
+        <v>2.268117785994007</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-6.087213048299902</v>
+        <v>-6.062826541467904</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.7157681839204337</v>
+        <v>0.725522786653233</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9903034259843706</v>
+        <v>-1.229527324547015</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.55682777196352</v>
+        <v>2.413293432825933</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.380133424795064</v>
+        <v>-5.355746917963065</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.9958129996620682</v>
+        <v>1.005567602394867</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9903034259843706</v>
+        <v>-1.229527324547015</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.554040738303219</v>
+        <v>2.410506399165632</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-5.130492394809112</v>
+        <v>-5.106105887977114</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.09601303554429</v>
+        <v>1.10576763827709</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.7406623959984189</v>
+        <v>-0.9798862945610636</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.704168980182631</v>
+        <v>2.560634641045044</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.875950495468036</v>
+        <v>-4.851563988636038</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.197196616501478</v>
+        <v>1.206951219234277</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.4861204966573434</v>
+        <v>-0.7253443952199881</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.856260941008034</v>
+        <v>2.712726601870447</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.642469273238437</v>
+        <v>-4.618082766406439</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.298513534231169</v>
+        <v>1.308268136963969</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.2526392744277448</v>
+        <v>-0.4918631729903895</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.004274103183645</v>
+        <v>2.860739764046058</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.462760743094565</v>
+        <v>-4.438374236262566</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.367504735975759</v>
+        <v>1.377259338708559</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.1954677702650487</v>
+        <v>-0.4346916688276934</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.035684795368303</v>
+        <v>2.892150456230717</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.330485269463678</v>
+        <v>-4.30609876263168</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.415782412175141</v>
+        <v>1.42553701490794</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.06319229663416204</v>
+        <v>-0.3024161951968067</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.110417566293862</v>
+        <v>2.966883227156276</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.139885594790526</v>
+        <v>-4.115499087958527</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.494837342732039</v>
+        <v>1.504591945464838</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.1274073780389908</v>
+        <v>-0.1118165205236539</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.227592431785391</v>
+        <v>3.084058092647804</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.890885796106945</v>
+        <v>-3.866499289274947</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.60734360342913</v>
+        <v>1.617098206161929</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.3764071767225715</v>
+        <v>0.1371832781599268</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.389898652219198</v>
+        <v>3.246364313081611</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.699506721246005</v>
+        <v>-3.675120214414007</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.555919303774287</v>
+        <v>1.565673906507086</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.5677862515835116</v>
+        <v>0.3285623530208669</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.376750167536544</v>
+        <v>3.233215828398956</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.420479425590378</v>
+        <v>-3.39609291875838</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.716074563913624</v>
+        <v>1.725829166646423</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.5677862515835116</v>
+        <v>0.3285623530208669</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.42529450941363</v>
+        <v>3.281760170276043</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.143741250919566</v>
+        <v>-3.119354744087568</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.830148845767944</v>
+        <v>1.839903448500743</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.7496029126934374</v>
+        <v>0.5103790141307927</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.53776351806558</v>
+        <v>3.394229178927993</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.016848844484496</v>
+        <v>-2.992462337652498</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.872191822088493</v>
+        <v>1.881946424821293</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6372714205658626</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.605184975673144</v>
+        <v>3.461650636535557</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.829261336574569</v>
+        <v>-2.804874829742571</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.940266213157371</v>
+        <v>1.95002081589017</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6372714205658626</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.59822436357805</v>
+        <v>3.454690024440464</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.587112943120711</v>
+        <v>-2.562726436288713</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.051587924920057</v>
+        <v>2.061342527652857</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6372714205658626</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.612686717959193</v>
+        <v>3.469152378821607</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.480039076745896</v>
+        <v>3.552768698126741</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.368210304324853</v>
+        <v>-2.354852206346957</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.133681100897595</v>
+        <v>2.139024340088754</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6372714205658626</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.607218838418389</v>
+        <v>3.463684499280802</v>
       </c>
     </row>
   </sheetData>
